--- a/docs/social media manager/social-content-planner.xlsx
+++ b/docs/social media manager/social-content-planner.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channels" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Idea bank" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Prompts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,10 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,7 +591,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[{"slug": "how-to-switch-broadband-uk", "title": "How to Switch Broadband Provider in the UK (2026)", "url": "https://broadbandpicker.co.uk/guides/how-to-switch-broadband-uk"}, {"slug": "best-broadband-deals-uk", "title": "Best Broadband Deals in the UK Right Now", "url": "https://broadbandpicker.co.uk/guides/best-broadband-deals-uk"}, {"slug": "broadband-deals-with-no-mid-contract-price-rise", "title": "Broadband Deals With No Mid-Contract Price Rise UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-with-no-mid-contract-price-rise"}, {"slug": "best-broadband-and-tv-deals", "title": "Best Broadband and TV Deals in the UK for 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-and-tv-deals"}, {"slug": "broadband-deals-under-20", "title": "Broadband Deals Under £20 UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-under-20"}, {"slug": "broadband-deals-with-cashback", "title": "Broadband Deals With Cashback UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-with-cashback"}, {"slug": "broadband-deals-with-no-setup-fee", "title": "Broadband Deals With No Setup Fee UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-with-no-setup-fee"}, {"slug": "best-rolling-monthly-broadband-deals", "title": "Best Rolling Monthly Broadband Deals UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-rolling-monthly-broadband-deals"}, {"slug": "full-fibre-broadband-explained", "title": "Full Fibre Broadband Explained: Is FTTP Worth It?", "url": "https://broadbandpicker.co.uk/guides/full-fibre-broadband-explained"}, {"slug": "broadband-speeds-explained", "title": "Broadband Speeds Explained: What Speed Do You Actually Need?", "url": "https://broadbandpicker.co.uk/guides/broadband-speeds-explained"}, {"slug": "cheapest-broadband-uk", "title": "Cheapest Broadband Deals in the UK 2026", "url": "https://broadbandpicker.co.uk/guides/cheapest-broadband-uk"}, {"slug": "best-broadband-for-working-from-home", "title": "Best Broadband for Working From Home UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-working-from-home"}, {"slug": "best-broadband-for-students", "title": "Best Broadband for Students UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-students"}, {"slug": "best-broadband-for-streaming", "title": "Best Broadband for Streaming UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-streaming"}, {"slug": "best-broadband-providers-uk", "title": "Best Broadband Providers UK 2026: Ranked and Reviewed", "url": "https://broadbandpicker.co.uk/guides/best-broadband-providers-uk"}, {"slug": "broadband-price-rises-2026", "title": "Broadband Price Rises 2026: Every Provider Explained", "url": "https://broadbandpicker.co.uk/guides/broadband-price-rises-2026"}, {"slug": "can-i-leave-broadband-early-after-price-rise", "title": "Can I Leave Broadband Early After a Price Rise? UK Rules Explained", "url": "https://broadbandpicker.co.uk/guides/can-i-leave-broadband-early-after-price-rise"}, {"slug": "broadband-without-phone-line", "title": "Broadband Without a Phone Line UK 2026: Your Full Options", "url": "https://broadbandpicker.co.uk/guides/broadband-without-phone-line"}, {"slug": "best-5g-home-broadband-uk", "title": "Best 5G Home Broadband UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-5g-home-broadband-uk"}, {"slug": "best-full-fibre-broadband-uk", "title": "Best Full Fibre Broadband UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-full-fibre-broadband-uk"}, {"slug": "best-broadband-for-gaming-uk", "title": "Best Broadband for Gaming UK 2026: Speed, Ping and Providers", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-gaming-uk"}, {"slug": "broadband-social-tariffs-uk", "title": "Broadband Social Tariffs UK 2026: Who Qualifies and How to Apply", "url": "https://broadbandpicker.co.uk/guides/broadband-social-tariffs-uk"}, {"slug": "broadband-moving-house", "title": "Broadband When Moving House UK 2026: Complete Checklist", "url": "https://broadbandpicker.co.uk/guides/broadband-moving-house"}, {"slug": "best-broadband-for-rural-areas-uk", "title": "Best Broadband for Rural Areas UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-rural-areas-uk"}, {"slug": "broadband-for-existing-customers", "title": "Best Broadband Deals for Existing Customers UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-for-existing-customers"}, {"slug": "one-touch-switching-explained", "title": "One Touch Switching Explained: How Broadband Switching Works in 2026", "url": "https://broadbandpicker.co.uk/guides/one-touch-switching-explained"}, {"slug": "broadband-contract-end-rights", "title": "Broadband Contract End Rights UK 2026: What Happens When Your Deal Ends", "url": "https://broadbandpicker.co.uk/guides/broadband-contract-end-rights"}, {"slug": "static-ip-business-broadband-explained", "title": "Static IP Business Broadb</t>
+          <t xml:space="preserve">[{"slug": "how-to-switch-broadband-uk", "title": "How to Switch Broadband Provider in the UK (2026)", "url": "https://broadbandpicker.co.uk/guides/how-to-switch-broadband-uk"}, {"slug": "broadband-complaints-and-ombudsman-uk", "title": "Broadband Complaints and Ombudsman: Your UK Rights", "url": "https://broadbandpicker.co.uk/guides/broadband-complaints-and-ombudsman-uk"}, {"slug": "best-broadband-deals-uk", "title": "Best Broadband Deals in the UK Right Now", "url": "https://broadbandpicker.co.uk/guides/best-broadband-deals-uk"}, {"slug": "broadband-deals-with-no-mid-contract-price-rise", "title": "Broadband Deals With No Mid-Contract Price Rise UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-with-no-mid-contract-price-rise"}, {"slug": "best-broadband-and-tv-deals", "title": "Best Broadband and TV Deals in the UK for 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-and-tv-deals"}, {"slug": "broadband-deals-under-20", "title": "Broadband Deals Under £20 UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-under-20"}, {"slug": "broadband-deals-with-cashback", "title": "Broadband Deals With Cashback UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-with-cashback"}, {"slug": "broadband-deals-with-no-setup-fee", "title": "Broadband Deals With No Setup Fee UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-deals-with-no-setup-fee"}, {"slug": "best-rolling-monthly-broadband-deals", "title": "Best Rolling Monthly Broadband Deals UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-rolling-monthly-broadband-deals"}, {"slug": "full-fibre-broadband-explained", "title": "Full Fibre Broadband Explained: Is FTTP Worth It?", "url": "https://broadbandpicker.co.uk/guides/full-fibre-broadband-explained"}, {"slug": "broadband-speeds-explained", "title": "Broadband Speeds Explained: What Speed Do You Actually Need?", "url": "https://broadbandpicker.co.uk/guides/broadband-speeds-explained"}, {"slug": "cheapest-broadband-uk", "title": "Cheapest Broadband Deals in the UK 2026", "url": "https://broadbandpicker.co.uk/guides/cheapest-broadband-uk"}, {"slug": "best-broadband-for-working-from-home", "title": "Best Broadband for Working From Home UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-working-from-home"}, {"slug": "best-broadband-for-students", "title": "Best Broadband for Students UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-students"}, {"slug": "best-broadband-for-streaming", "title": "Best Broadband for Streaming UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-streaming"}, {"slug": "best-broadband-providers-uk", "title": "Best Broadband Providers UK 2026: Ranked and Reviewed", "url": "https://broadbandpicker.co.uk/guides/best-broadband-providers-uk"}, {"slug": "broadband-price-rises-2026", "title": "Broadband Price Rises 2026: Every Provider Explained", "url": "https://broadbandpicker.co.uk/guides/broadband-price-rises-2026"}, {"slug": "can-i-leave-broadband-early-after-price-rise", "title": "Can I Leave Broadband Early After a Price Rise? UK Rules Explained", "url": "https://broadbandpicker.co.uk/guides/can-i-leave-broadband-early-after-price-rise"}, {"slug": "broadband-without-phone-line", "title": "Broadband Without a Phone Line UK 2026: Your Full Options", "url": "https://broadbandpicker.co.uk/guides/broadband-without-phone-line"}, {"slug": "best-5g-home-broadband-uk", "title": "Best 5G Home Broadband UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-5g-home-broadband-uk"}, {"slug": "best-full-fibre-broadband-uk", "title": "Best Full Fibre Broadband UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-full-fibre-broadband-uk"}, {"slug": "best-broadband-for-gaming-uk", "title": "Best Broadband for Gaming UK 2026: Speed, Ping and Providers", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-gaming-uk"}, {"slug": "broadband-social-tariffs-uk", "title": "Broadband Social Tariffs UK 2026: Who Qualifies and How to Apply", "url": "https://broadbandpicker.co.uk/guides/broadband-social-tariffs-uk"}, {"slug": "broadband-moving-house", "title": "Broadband When Moving House UK 2026: Complete Checklist", "url": "https://broadbandpicker.co.uk/guides/broadband-moving-house"}, {"slug": "best-broadband-for-rural-areas-uk", "title": "Best Broadband for Rural Areas UK 2026", "url": "https://broadbandpicker.co.uk/guides/best-broadband-for-rural-areas-uk"}, {"slug": "broadband-for-existing-customers", "title": "Best Broadband Deals for Existing Customers UK 2026", "url": "https://broadbandpicker.co.uk/guides/broadband-for-existing-customers"}, {"slug": "one-touch-switching-explained", "title": "One Touch Switching Explained: How Broadband Switching Works in 2026", "url": "https://broadbandpicker.co.uk/guides/one-touch-switching-explained"}, {"slug": "broadband-contract-end-rights", "title": "Broadband Contract End Rights UK 2026: </t>
         </is>
       </c>
     </row>
@@ -6456,4 +6460,4177 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E126"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prompt (paste into ChatGPT / DALL-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Loyalty is a hostage situation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two fake bills side by side. Left labelled NEW CUSTOMER in sky blue. Right labelled LOYAL CUSTOMER in angry red-navy. Same tiny print energy as a real ISP email.
+On-screen text, large and bold, exactly as written, no other wording added: "New customer: £19" "You: £41" "That's not loyalty." "That's a hostage situation."
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Anton or Impact for the joke; Inter Bold for the end card.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real customer's bill; Don't name a fake official tariff. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X-001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Loyalty is a hostage situation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two fake bills side by side. Left labelled NEW CUSTOMER in sky blue. Right labelled LOYAL CUSTOMER in angry red-navy. Same tiny print energy as a real ISP email.
+On-screen text, large and bold, exactly as written, no other wording added: "New customer: £19" "You: £41" "That's not loyalty." "That's a hostage situation."
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Anton or Impact for the joke; Inter Bold for the end card.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real customer's bill; Don't name a fake official tariff. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X-001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Loyalty is a hostage situation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two fake bills side by side. Left labelled NEW CUSTOMER in sky blue. Right labelled LOYAL CUSTOMER in angry red-navy. Same tiny print energy as a real ISP email.
+On-screen text, large and bold, exactly as written, no other wording added: "New customer: £19" "You: £41" "That's not loyalty." "That's a hostage situation."
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Anton or Impact for the joke; Inter Bold for the end card.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real customer's bill; Don't name a fake official tariff. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>X-001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Loyalty is a hostage situation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two fake bills side by side. Left labelled NEW CUSTOMER in sky blue. Right labelled LOYAL CUSTOMER in angry red-navy. Same tiny print energy as a real ISP email.
+On-screen text, large and bold, exactly as written, no other wording added: "New customer: £19" "You: £41" "That's not loyalty." "That's a hostage situation."
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Anton or Impact for the joke; Inter Bold for the end card.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real customer's bill; Don't name a fake official tariff. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X-001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Loyalty is a hostage situation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two fake bills side by side. Left labelled NEW CUSTOMER in sky blue. Right labelled LOYAL CUSTOMER in angry red-navy. Same tiny print energy as a real ISP email.
+On-screen text, large and bold, exactly as written, no other wording added: "New customer: £19" "You: £41" "That's not loyalty." "That's a hostage situation."
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Anton or Impact for the joke; Inter Bold for the end card.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real customer's bill; Don't name a fake official tariff. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>X-002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yellow warning of buffering</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Yellow warning triangle, map of the UK with a blob over 'wherever you live', ticker: BUFFERING. Bottom: 'Check your postcode, not the clouds.'
+On-screen text, large and bold, exactly as written, no other wording added: "YELLOW WARNING OF BUFFERING" "From 7pm until you give up" "Likely: Netflix, Zoom, dignity"
+Colour palette: Warning yellow #F4D35E on navy, white type, sky-blue BroadbandPicker footer.
+Typography style: A Met-Office-ish sans. Keep it official-looking then undercut it.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use the real Met Office trademark lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X-002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yellow warning of buffering</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Yellow warning triangle, map of the UK with a blob over 'wherever you live', ticker: BUFFERING. Bottom: 'Check your postcode, not the clouds.'
+On-screen text, large and bold, exactly as written, no other wording added: "YELLOW WARNING OF BUFFERING" "From 7pm until you give up" "Likely: Netflix, Zoom, dignity"
+Colour palette: Warning yellow #F4D35E on navy, white type, sky-blue BroadbandPicker footer.
+Typography style: A Met-Office-ish sans. Keep it official-looking then undercut it.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use the real Met Office trademark lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>X-002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yellow warning of buffering</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Yellow warning triangle, map of the UK with a blob over 'wherever you live', ticker: BUFFERING. Bottom: 'Check your postcode, not the clouds.'
+On-screen text, large and bold, exactly as written, no other wording added: "YELLOW WARNING OF BUFFERING" "From 7pm until you give up" "Likely: Netflix, Zoom, dignity"
+Colour palette: Warning yellow #F4D35E on navy, white type, sky-blue BroadbandPicker footer.
+Typography style: A Met-Office-ish sans. Keep it official-looking then undercut it.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use the real Met Office trademark lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>X-002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yellow warning of buffering</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Yellow warning triangle, map of the UK with a blob over 'wherever you live', ticker: BUFFERING. Bottom: 'Check your postcode, not the clouds.'
+On-screen text, large and bold, exactly as written, no other wording added: "YELLOW WARNING OF BUFFERING" "From 7pm until you give up" "Likely: Netflix, Zoom, dignity"
+Colour palette: Warning yellow #F4D35E on navy, white type, sky-blue BroadbandPicker footer.
+Typography style: A Met-Office-ish sans. Keep it official-looking then undercut it.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use the real Met Office trademark lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>X-002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yellow warning of buffering</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Yellow warning triangle, map of the UK with a blob over 'wherever you live', ticker: BUFFERING. Bottom: 'Check your postcode, not the clouds.'
+On-screen text, large and bold, exactly as written, no other wording added: "YELLOW WARNING OF BUFFERING" "From 7pm until you give up" "Likely: Netflix, Zoom, dignity"
+Colour palette: Warning yellow #F4D35E on navy, white type, sky-blue BroadbandPicker footer.
+Typography style: A Met-Office-ish sans. Keep it official-looking then undercut it.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use the real Met Office trademark lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>X-003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Keep calm and restart the router</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Classic cream poster, crown replaced with the BroadbandPicker wifi mark, red strip KEEP CALM AND RESTART THE ROUTER.
+On-screen text, large and bold, exactly as written, no other wording added: "KEEP CALM" "AND" "RESTART THE ROUTER"
+Colour palette: Ministry cream, poster red, navy type, sky wifi-mark.
+Typography style: A Times-like serif or a poster gothic. Not Inter for this one.
+Logo placement: Wifi-mark as the 'crown'. Wordmark tiny at the bottom.
+Avoid: Don't add six other jokes on the poster. One line.. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>X-003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Keep calm and restart the router</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Classic cream poster, crown replaced with the BroadbandPicker wifi mark, red strip KEEP CALM AND RESTART THE ROUTER.
+On-screen text, large and bold, exactly as written, no other wording added: "KEEP CALM" "AND" "RESTART THE ROUTER"
+Colour palette: Ministry cream, poster red, navy type, sky wifi-mark.
+Typography style: A Times-like serif or a poster gothic. Not Inter for this one.
+Logo placement: Wifi-mark as the 'crown'. Wordmark tiny at the bottom.
+Avoid: Don't add six other jokes on the poster. One line.. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>X-003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Keep calm and restart the router</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Classic cream poster, crown replaced with the BroadbandPicker wifi mark, red strip KEEP CALM AND RESTART THE ROUTER.
+On-screen text, large and bold, exactly as written, no other wording added: "KEEP CALM" "AND" "RESTART THE ROUTER"
+Colour palette: Ministry cream, poster red, navy type, sky wifi-mark.
+Typography style: A Times-like serif or a poster gothic. Not Inter for this one.
+Logo placement: Wifi-mark as the 'crown'. Wordmark tiny at the bottom.
+Avoid: Don't add six other jokes on the poster. One line.. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>X-003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Keep calm and restart the router</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Classic cream poster, crown replaced with the BroadbandPicker wifi mark, red strip KEEP CALM AND RESTART THE ROUTER.
+On-screen text, large and bold, exactly as written, no other wording added: "KEEP CALM" "AND" "RESTART THE ROUTER"
+Colour palette: Ministry cream, poster red, navy type, sky wifi-mark.
+Typography style: A Times-like serif or a poster gothic. Not Inter for this one.
+Logo placement: Wifi-mark as the 'crown'. Wordmark tiny at the bottom.
+Avoid: Don't add six other jokes on the poster. One line.. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>X-003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Keep calm and restart the router</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Classic cream poster, crown replaced with the BroadbandPicker wifi mark, red strip KEEP CALM AND RESTART THE ROUTER.
+On-screen text, large and bold, exactly as written, no other wording added: "KEEP CALM" "AND" "RESTART THE ROUTER"
+Colour palette: Ministry cream, poster red, navy type, sky wifi-mark.
+Typography style: A Times-like serif or a poster gothic. Not Inter for this one.
+Logo placement: Wifi-mark as the 'crown'. Wordmark tiny at the bottom.
+Avoid: Don't add six other jokes on the poster. One line.. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>X-004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Up to</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Giant 'UP TO 67 Mbps' in advert-land, camera zooms into microscopic footnotes until it becomes a novel.
+On-screen text, large and bold, exactly as written, no other wording added: "UP TO 67 Mbps" "*up to a biscuit" "*up to your nan's 'soon'"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Advert grotesk, then Courier for the footnotes.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a real provider's current advertised number. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>X-004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Up to</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Giant 'UP TO 67 Mbps' in advert-land, camera zooms into microscopic footnotes until it becomes a novel.
+On-screen text, large and bold, exactly as written, no other wording added: "UP TO 67 Mbps" "*up to a biscuit" "*up to your nan's 'soon'"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Advert grotesk, then Courier for the footnotes.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a real provider's current advertised number. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>X-004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Up to</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Giant 'UP TO 67 Mbps' in advert-land, camera zooms into microscopic footnotes until it becomes a novel.
+On-screen text, large and bold, exactly as written, no other wording added: "UP TO 67 Mbps" "*up to a biscuit" "*up to your nan's 'soon'"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Advert grotesk, then Courier for the footnotes.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a real provider's current advertised number. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>X-005</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>89th minute</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Over-the-sofa POV, match on TV, buffering spinner, cut to a man kneeling before a router like it's a shrine.
+On-screen text, large and bold, exactly as written, no other wording added: "89:00" "buffering" "the national sport"
+Colour palette: Warm living-room, then navy end card.
+Typography style: Scoreboard type for the time, Inter for the caption.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use Premier League footage. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>X-005</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>89th minute</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Over-the-sofa POV, match on TV, buffering spinner, cut to a man kneeling before a router like it's a shrine.
+On-screen text, large and bold, exactly as written, no other wording added: "89:00" "buffering" "the national sport"
+Colour palette: Warm living-room, then navy end card.
+Typography style: Scoreboard type for the time, Inter for the caption.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use Premier League footage. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>X-005</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>89th minute</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Over-the-sofa POV, match on TV, buffering spinner, cut to a man kneeling before a router like it's a shrine.
+On-screen text, large and bold, exactly as written, no other wording added: "89:00" "buffering" "the national sport"
+Colour palette: Warm living-room, then navy end card.
+Typography style: Scoreboard type for the time, Inter for the caption.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use Premier League footage. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>X-006</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Socrates pays the bill</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Marble bust with a cheap ISP router photoshopped as a laurel. Quote in a literary serif. Tiny 'probably' in sky blue.
+On-screen text, large and bold, exactly as written, no other wording added: "The unexamined broadband bill is not worth paying." "— Socrates, probably"
+Colour palette: Statue grey, navy, sky pull-quote marks.
+Typography style: Playfair / Source Serif for the quote, Inter for the probably.
+Logo placement: Small mark bottom-right, plenty of margin.
+Avoid: Don't make the bust a recognisable living person. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>X-006</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Socrates pays the bill</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Marble bust with a cheap ISP router photoshopped as a laurel. Quote in a literary serif. Tiny 'probably' in sky blue.
+On-screen text, large and bold, exactly as written, no other wording added: "The unexamined broadband bill is not worth paying." "— Socrates, probably"
+Colour palette: Statue grey, navy, sky pull-quote marks.
+Typography style: Playfair / Source Serif for the quote, Inter for the probably.
+Logo placement: Small mark bottom-right, plenty of margin.
+Avoid: Don't make the bust a recognisable living person. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-006</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Socrates pays the bill</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Marble bust with a cheap ISP router photoshopped as a laurel. Quote in a literary serif. Tiny 'probably' in sky blue.
+On-screen text, large and bold, exactly as written, no other wording added: "The unexamined broadband bill is not worth paying." "— Socrates, probably"
+Colour palette: Statue grey, navy, sky pull-quote marks.
+Typography style: Playfair / Source Serif for the quote, Inter for the probably.
+Logo placement: Small mark bottom-right, plenty of margin.
+Avoid: Don't make the bust a recognisable living person. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>X-006</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Socrates pays the bill</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Marble bust with a cheap ISP router photoshopped as a laurel. Quote in a literary serif. Tiny 'probably' in sky blue.
+On-screen text, large and bold, exactly as written, no other wording added: "The unexamined broadband bill is not worth paying." "— Socrates, probably"
+Colour palette: Statue grey, navy, sky pull-quote marks.
+Typography style: Playfair / Source Serif for the quote, Inter for the probably.
+Logo placement: Small mark bottom-right, plenty of margin.
+Avoid: Don't make the bust a recognisable living person. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>X-007</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Router in the cupboard</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Phone-torch tour of a British under-stairs cupboard. Reveal: router, blinking, under a pile of coats. Caption like Location Location Location.
+On-screen text, large and bold, exactly as written, no other wording added: "The master bedroom of your Wi-Fi" "Period features: damp, beans, 12 Mbps"
+Colour palette: Documentary torchlight, then clean end card.
+Typography style: Channel 4 documentary lower-third.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't film someone else's house without permission. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>X-007</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Router in the cupboard</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Phone-torch tour of a British under-stairs cupboard. Reveal: router, blinking, under a pile of coats. Caption like Location Location Location.
+On-screen text, large and bold, exactly as written, no other wording added: "The master bedroom of your Wi-Fi" "Period features: damp, beans, 12 Mbps"
+Colour palette: Documentary torchlight, then clean end card.
+Typography style: Channel 4 documentary lower-third.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't film someone else's house without permission. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>X-007</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Router in the cupboard</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Phone-torch tour of a British under-stairs cupboard. Reveal: router, blinking, under a pile of coats. Caption like Location Location Location.
+On-screen text, large and bold, exactly as written, no other wording added: "The master bedroom of your Wi-Fi" "Period features: damp, beans, 12 Mbps"
+Colour palette: Documentary torchlight, then clean end card.
+Typography style: Channel 4 documentary lower-third.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't film someone else's house without permission. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>X-008</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Engineer window</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A calendar where Monday–Sunday are all highlighted. Sticky note: ENGINEER. A flask and a folding chair on the drive.
+On-screen text, large and bold, exactly as written, no other wording added: "Appointment" "8am–6pm" "so… Tuesday?"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Utility sans, like a job sheet.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real Openreach uniform in a mocking way that implies a real engineer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>X-008</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Engineer window</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A calendar where Monday–Sunday are all highlighted. Sticky note: ENGINEER. A flask and a folding chair on the drive.
+On-screen text, large and bold, exactly as written, no other wording added: "Appointment" "8am–6pm" "so… Tuesday?"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Utility sans, like a job sheet.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real Openreach uniform in a mocking way that implies a real engineer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>X-008</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Engineer window</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A calendar where Monday–Sunday are all highlighted. Sticky note: ENGINEER. A flask and a folding chair on the drive.
+On-screen text, large and bold, exactly as written, no other wording added: "Appointment" "8am–6pm" "so… Tuesday?"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Utility sans, like a job sheet.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real Openreach uniform in a mocking way that implies a real engineer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>X-008</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Engineer window</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A calendar where Monday–Sunday are all highlighted. Sticky note: ENGINEER. A flask and a folding chair on the drive.
+On-screen text, large and bold, exactly as written, no other wording added: "Appointment" "8am–6pm" "so… Tuesday?"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Utility sans, like a job sheet.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real Openreach uniform in a mocking way that implies a real engineer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>X-009</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Full fibre is coming</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A weathered 'Coming soon: full fibre' council-style sign overgrown with ivy. Date on the sign: 2014.
+On-screen text, large and bold, exactly as written, no other wording added: "COMING SOON" "full fibre" "est. any parliament now"
+Colour palette: Council green, rust, navy caption bar.
+Typography style: Highways signage type.
+Logo placement: Bar at the bottom: Check the postcode, not the sign.
+Avoid: Don't fake an official local-authority crest. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>X-009</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Full fibre is coming</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A weathered 'Coming soon: full fibre' council-style sign overgrown with ivy. Date on the sign: 2014.
+On-screen text, large and bold, exactly as written, no other wording added: "COMING SOON" "full fibre" "est. any parliament now"
+Colour palette: Council green, rust, navy caption bar.
+Typography style: Highways signage type.
+Logo placement: Bar at the bottom: Check the postcode, not the sign.
+Avoid: Don't fake an official local-authority crest. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>X-009</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Full fibre is coming</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A weathered 'Coming soon: full fibre' council-style sign overgrown with ivy. Date on the sign: 2014.
+On-screen text, large and bold, exactly as written, no other wording added: "COMING SOON" "full fibre" "est. any parliament now"
+Colour palette: Council green, rust, navy caption bar.
+Typography style: Highways signage type.
+Logo placement: Bar at the bottom: Check the postcode, not the sign.
+Avoid: Don't fake an official local-authority crest. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>X-010</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Drake / out of contract</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Standard two-panel Drake. Top: crumpled bill. Bottom: postcode checker screenshot (use BroadbandPicker UI, not a competitor).
+On-screen text, large and bold, exactly as written, no other wording added: "Paying the loyalty price" "Four minutes on BroadbandPicker"
+Colour palette: Meme-native, end card in brand colours.
+Typography style: Impact for panels, Inter on the end card.
+Logo placement: Only on the accept panel as the UI, plus end card.
+Avoid: Don't use uncleared celebrity likeness if you can shoot an original 'nah/yeah' with a staffer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>X-010</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Drake / out of contract</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Standard two-panel Drake. Top: crumpled bill. Bottom: postcode checker screenshot (use BroadbandPicker UI, not a competitor).
+On-screen text, large and bold, exactly as written, no other wording added: "Paying the loyalty price" "Four minutes on BroadbandPicker"
+Colour palette: Meme-native, end card in brand colours.
+Typography style: Impact for panels, Inter on the end card.
+Logo placement: Only on the accept panel as the UI, plus end card.
+Avoid: Don't use uncleared celebrity likeness if you can shoot an original 'nah/yeah' with a staffer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>X-010</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Drake / out of contract</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Standard two-panel Drake. Top: crumpled bill. Bottom: postcode checker screenshot (use BroadbandPicker UI, not a competitor).
+On-screen text, large and bold, exactly as written, no other wording added: "Paying the loyalty price" "Four minutes on BroadbandPicker"
+Colour palette: Meme-native, end card in brand colours.
+Typography style: Impact for panels, Inter on the end card.
+Logo placement: Only on the accept panel as the UI, plus end card.
+Avoid: Don't use uncleared celebrity likeness if you can shoot an original 'nah/yeah' with a staffer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>X-010</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Drake / out of contract</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Standard two-panel Drake. Top: crumpled bill. Bottom: postcode checker screenshot (use BroadbandPicker UI, not a competitor).
+On-screen text, large and bold, exactly as written, no other wording added: "Paying the loyalty price" "Four minutes on BroadbandPicker"
+Colour palette: Meme-native, end card in brand colours.
+Typography style: Impact for panels, Inter on the end card.
+Logo placement: Only on the accept panel as the UI, plus end card.
+Avoid: Don't use uncleared celebrity likeness if you can shoot an original 'nah/yeah' with a staffer. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>X-011</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fibre I barely know her</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two doors. One ornate 'FULL FIBRE'. One labelled 'fibre' in Comic Sans, leading to a muddy alley.
+On-screen text, large and bold, exactly as written, no other wording added: "Fibre" "Full fibre" "One of these still involves the 1990s"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Clean Inter on slides 2–3 where you actually explain it.
+Logo placement: Slide 3.
+Avoid: Don't leave people thinking all 'fibre' is a scam — some FTTC is fine for light use. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>X-011</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fibre I barely know her</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two doors. One ornate 'FULL FIBRE'. One labelled 'fibre' in Comic Sans, leading to a muddy alley.
+On-screen text, large and bold, exactly as written, no other wording added: "Fibre" "Full fibre" "One of these still involves the 1990s"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Clean Inter on slides 2–3 where you actually explain it.
+Logo placement: Slide 3.
+Avoid: Don't leave people thinking all 'fibre' is a scam — some FTTC is fine for light use. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>X-011</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fibre I barely know her</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two doors. One ornate 'FULL FIBRE'. One labelled 'fibre' in Comic Sans, leading to a muddy alley.
+On-screen text, large and bold, exactly as written, no other wording added: "Fibre" "Full fibre" "One of these still involves the 1990s"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Clean Inter on slides 2–3 where you actually explain it.
+Logo placement: Slide 3.
+Avoid: Don't leave people thinking all 'fibre' is a scam — some FTTC is fine for light use. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>X-012</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Flatshare FIFA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Top-down cheap CCTV vibe of a student kitchen. Each person labelled with the bandwidth they're stealing. FIFA lad has a halo of lag.
+On-screen text, large and bold, exactly as written, no other wording added: "National Grid, but for arguments" "Who touched the QoS settings"
+Colour palette: Sickly fluorescent, then navy end card.
+Typography style: CCTV timestamp font.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't film real students without releases. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>X-012</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Flatshare FIFA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Top-down cheap CCTV vibe of a student kitchen. Each person labelled with the bandwidth they're stealing. FIFA lad has a halo of lag.
+On-screen text, large and bold, exactly as written, no other wording added: "National Grid, but for arguments" "Who touched the QoS settings"
+Colour palette: Sickly fluorescent, then navy end card.
+Typography style: CCTV timestamp font.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't film real students without releases. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>X-012</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Flatshare FIFA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Top-down cheap CCTV vibe of a student kitchen. Each person labelled with the bandwidth they're stealing. FIFA lad has a halo of lag.
+On-screen text, large and bold, exactly as written, no other wording added: "National Grid, but for arguments" "Who touched the QoS settings"
+Colour palette: Sickly fluorescent, then navy end card.
+Typography style: CCTV timestamp font.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't film real students without releases. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>X-013</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Social tariff scandal</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Drop the meme face. Clean navy slides, big type, one fact each, final slide is the URL. This is the adult in the room.
+On-screen text, large and bold, exactly as written, no other wording added: "If you're on certain benefits, cheaper broadband exists" "Most eligible people have never heard of it" "It's called a social tariff" "We explain who qualifies, without the waffle"
+Colour palette: Navy #0F172A, white type, green #22C55E ticks. No yellow jokes.
+Typography style: Inter ExtraBold headlines, Inter Regular body.
+Logo placement: On every slide, small, because this is branded public service.
+Avoid: Don't put a clown meme on this one. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>X-013</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Social tariff scandal</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Drop the meme face. Clean navy slides, big type, one fact each, final slide is the URL. This is the adult in the room.
+On-screen text, large and bold, exactly as written, no other wording added: "If you're on certain benefits, cheaper broadband exists" "Most eligible people have never heard of it" "It's called a social tariff" "We explain who qualifies, without the waffle"
+Colour palette: Navy #0F172A, white type, green #22C55E ticks. No yellow jokes.
+Typography style: Inter ExtraBold headlines, Inter Regular body.
+Logo placement: On every slide, small, because this is branded public service.
+Avoid: Don't put a clown meme on this one. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>X-013</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Social tariff scandal</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Drop the meme face. Clean navy slides, big type, one fact each, final slide is the URL. This is the adult in the room.
+On-screen text, large and bold, exactly as written, no other wording added: "If you're on certain benefits, cheaper broadband exists" "Most eligible people have never heard of it" "It's called a social tariff" "We explain who qualifies, without the waffle"
+Colour palette: Navy #0F172A, white type, green #22C55E ticks. No yellow jokes.
+Typography style: Inter ExtraBold headlines, Inter Regular body.
+Logo placement: On every slide, small, because this is branded public service.
+Avoid: Don't put a clown meme on this one. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>X-014</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ask not what your ISP can do</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Presidential speech desk. Behind: not a flag, a router with a sad orange light.
+On-screen text, large and bold, exactly as written, no other wording added: "HAVE YOU TRIED" "TURNING IT OFF" "AND ON AGAIN"
+Colour palette: Navy, red stripe as a visual gag not a party colour, sky wifi-mark as a lapel pin.
+Typography style: Inscribed serif.
+Logo placement: Lapel-pin wifi mark + bottom URL.
+Avoid: Don't use an official US or UK government lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>X-014</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ask not what your ISP can do</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Presidential speech desk. Behind: not a flag, a router with a sad orange light.
+On-screen text, large and bold, exactly as written, no other wording added: "HAVE YOU TRIED" "TURNING IT OFF" "AND ON AGAIN"
+Colour palette: Navy, red stripe as a visual gag not a party colour, sky wifi-mark as a lapel pin.
+Typography style: Inscribed serif.
+Logo placement: Lapel-pin wifi mark + bottom URL.
+Avoid: Don't use an official US or UK government lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>X-014</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ask not what your ISP can do</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Presidential speech desk. Behind: not a flag, a router with a sad orange light.
+On-screen text, large and bold, exactly as written, no other wording added: "HAVE YOU TRIED" "TURNING IT OFF" "AND ON AGAIN"
+Colour palette: Navy, red stripe as a visual gag not a party colour, sky wifi-mark as a lapel pin.
+Typography style: Inscribed serif.
+Logo placement: Lapel-pin wifi mark + bottom URL.
+Avoid: Don't use an official US or UK government lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>X-014</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ask not what your ISP can do</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Presidential speech desk. Behind: not a flag, a router with a sad orange light.
+On-screen text, large and bold, exactly as written, no other wording added: "HAVE YOU TRIED" "TURNING IT OFF" "AND ON AGAIN"
+Colour palette: Navy, red stripe as a visual gag not a party colour, sky wifi-mark as a lapel pin.
+Typography style: Inscribed serif.
+Logo placement: Lapel-pin wifi mark + bottom URL.
+Avoid: Don't use an official US or UK government lockup. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>X-015</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bandwidth like a British summer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Kiss Me Quick postcard: deckchairs, grey sky, a speed-test result stamped like a passport: 11 Mbps.
+On-screen text, large and bold, exactly as written, no other wording added: "WISH YOU WEREN'T HERE" "bandwidth as brief as the summer"
+Colour palette: Faded postcard reds, navy caption.
+Typography style: Retro script + Inter.
+Logo placement: Stamp in the corner using the wifi mark.
+Avoid: Don't use a real person's holiday photo. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>X-015</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bandwidth like a British summer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Kiss Me Quick postcard: deckchairs, grey sky, a speed-test result stamped like a passport: 11 Mbps.
+On-screen text, large and bold, exactly as written, no other wording added: "WISH YOU WEREN'T HERE" "bandwidth as brief as the summer"
+Colour palette: Faded postcard reds, navy caption.
+Typography style: Retro script + Inter.
+Logo placement: Stamp in the corner using the wifi mark.
+Avoid: Don't use a real person's holiday photo. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>X-015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bandwidth like a British summer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Kiss Me Quick postcard: deckchairs, grey sky, a speed-test result stamped like a passport: 11 Mbps.
+On-screen text, large and bold, exactly as written, no other wording added: "WISH YOU WEREN'T HERE" "bandwidth as brief as the summer"
+Colour palette: Faded postcard reds, navy caption.
+Typography style: Retro script + Inter.
+Logo placement: Stamp in the corner using the wifi mark.
+Avoid: Don't use a real person's holiday photo. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>X-016</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>April, the other tax month</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A British fridge: council tax letter, broadband rise letter, a faded photo of France.
+On-screen text, large and bold, exactly as written, no other wording added: "April" "the other tax month" "You can still leave"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Last slide.
+Avoid: Don't tell people they can always leave fee-free — that's not always true. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>X-016</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>April, the other tax month</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A British fridge: council tax letter, broadband rise letter, a faded photo of France.
+On-screen text, large and bold, exactly as written, no other wording added: "April" "the other tax month" "You can still leave"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Last slide.
+Avoid: Don't tell people they can always leave fee-free — that's not always true. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>X-016</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>April, the other tax month</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A British fridge: council tax letter, broadband rise letter, a faded photo of France.
+On-screen text, large and bold, exactly as written, no other wording added: "April" "the other tax month" "You can still leave"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Last slide.
+Avoid: Don't tell people they can always leave fee-free — that's not always true. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>X-016</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>April, the other tax month</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A British fridge: council tax letter, broadband rise letter, a faded photo of France.
+On-screen text, large and bold, exactly as written, no other wording added: "April" "the other tax month" "You can still leave"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Last slide.
+Avoid: Don't tell people they can always leave fee-free — that's not always true. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>X-016</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>April, the other tax month</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: A British fridge: council tax letter, broadband rise letter, a faded photo of France.
+On-screen text, large and bold, exactly as written, no other wording added: "April" "the other tax month" "You can still leave"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Last slide.
+Avoid: Don't tell people they can always leave fee-free — that's not always true. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>X-017</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Wi-Fi name personality test</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iOS/Android Wi-Fi list with joke names. A finger hovers, never connects.
+On-screen text, large and bold, exactly as written, no other wording added: "Choose your fighter" "password in the comments = banned"
+Colour palette: OS-native then brand end card.
+Typography style: SF/Roboto for the fake OS, Inter at the end.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't include a real neighbour's network from a captured screenshot. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>X-017</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Wi-Fi name personality test</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iOS/Android Wi-Fi list with joke names. A finger hovers, never connects.
+On-screen text, large and bold, exactly as written, no other wording added: "Choose your fighter" "password in the comments = banned"
+Colour palette: OS-native then brand end card.
+Typography style: SF/Roboto for the fake OS, Inter at the end.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't include a real neighbour's network from a captured screenshot. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>X-017</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Wi-Fi name personality test</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iOS/Android Wi-Fi list with joke names. A finger hovers, never connects.
+On-screen text, large and bold, exactly as written, no other wording added: "Choose your fighter" "password in the comments = banned"
+Colour palette: OS-native then brand end card.
+Typography style: SF/Roboto for the fake OS, Inter at the end.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't include a real neighbour's network from a captured screenshot. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>X-017</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Wi-Fi name personality test</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iOS/Android Wi-Fi list with joke names. A finger hovers, never connects.
+On-screen text, large and bold, exactly as written, no other wording added: "Choose your fighter" "password in the comments = banned"
+Colour palette: OS-native then brand end card.
+Typography style: SF/Roboto for the fake OS, Inter at the end.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't include a real neighbour's network from a captured screenshot. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>X-018</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Speed you actually need</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Slide 1 joke, slides 2–5 useful table, slide 6 Broadband Match CTA. Let the joke earn the table.
+On-screen text, large and bold, exactly as written, no other wording added: "Gigabit is a personality" "Here's what you actually need"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter throughout. This one should look like the website grew a sense of humour.
+Logo placement: All slides, small.
+Avoid: Don't invent a 'perfect Mbps' for every home. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>X-018</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Speed you actually need</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Slide 1 joke, slides 2–5 useful table, slide 6 Broadband Match CTA. Let the joke earn the table.
+On-screen text, large and bold, exactly as written, no other wording added: "Gigabit is a personality" "Here's what you actually need"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter throughout. This one should look like the website grew a sense of humour.
+Logo placement: All slides, small.
+Avoid: Don't invent a 'perfect Mbps' for every home. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>X-018</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Speed you actually need</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Slide 1 joke, slides 2–5 useful table, slide 6 Broadband Match CTA. Let the joke earn the table.
+On-screen text, large and bold, exactly as written, no other wording added: "Gigabit is a personality" "Here's what you actually need"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter throughout. This one should look like the website grew a sense of humour.
+Logo placement: All slides, small.
+Avoid: Don't invent a 'perfect Mbps' for every home. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>X-019</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Same copper, different jumper</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Spider-Man pointing meme energy, but two identical Openreach cabinets wearing different knitted jumpers with brand-ish colours (not logos).
+On-screen text, large and bold, exactly as written, no other wording added: "It's the same cabinet" "Different jumper"
+Colour palette: Street photography + brand bar.
+Typography style: Inter.
+Logo placement: Bar.
+Avoid: Don't put real ISP logos on the jumpers. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>X-019</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Same copper, different jumper</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Spider-Man pointing meme energy, but two identical Openreach cabinets wearing different knitted jumpers with brand-ish colours (not logos).
+On-screen text, large and bold, exactly as written, no other wording added: "It's the same cabinet" "Different jumper"
+Colour palette: Street photography + brand bar.
+Typography style: Inter.
+Logo placement: Bar.
+Avoid: Don't put real ISP logos on the jumpers. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>X-019</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Same copper, different jumper</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Spider-Man pointing meme energy, but two identical Openreach cabinets wearing different knitted jumpers with brand-ish colours (not logos).
+On-screen text, large and bold, exactly as written, no other wording added: "It's the same cabinet" "Different jumper"
+Colour palette: Street photography + brand bar.
+Typography style: Inter.
+Logo placement: Bar.
+Avoid: Don't put real ISP logos on the jumpers. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>X-020</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Zoom, you're muted, no it's the line</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: 2x2 grid. Three crisp colleagues. One pixelated impressionist painting that used to be a man in Stevenage.
+On-screen text, large and bold, exactly as written, no other wording added: "You're muted" "That's the broadband"
+Colour palette: App greys, then brand end card.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't mock a real person's appearance; keep it about the pixels. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>X-020</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Zoom, you're muted, no it's the line</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: 2x2 grid. Three crisp colleagues. One pixelated impressionist painting that used to be a man in Stevenage.
+On-screen text, large and bold, exactly as written, no other wording added: "You're muted" "That's the broadband"
+Colour palette: App greys, then brand end card.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't mock a real person's appearance; keep it about the pixels. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>X-020</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Zoom, you're muted, no it's the line</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: 2x2 grid. Three crisp colleagues. One pixelated impressionist painting that used to be a man in Stevenage.
+On-screen text, large and bold, exactly as written, no other wording added: "You're muted" "That's the broadband"
+Colour palette: App greys, then brand end card.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't mock a real person's appearance; keep it about the pixels. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>X-021</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Packet loss packed lunch</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iMessage conversation with 'Your ISP'. Grey bubble: 'it's not you it's packet loss.'
+On-screen text, large and bold, exactly as written, no other wording added: "Delivered" "read at 19:42" "during the football, obviously"
+Colour palette: iMessage blue/grey, navy end card.
+Typography style: SF-like.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use Apple's trademarked iMessage lockup in ads — organic pastiche is the usual risk level. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>X-021</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Packet loss packed lunch</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iMessage conversation with 'Your ISP'. Grey bubble: 'it's not you it's packet loss.'
+On-screen text, large and bold, exactly as written, no other wording added: "Delivered" "read at 19:42" "during the football, obviously"
+Colour palette: iMessage blue/grey, navy end card.
+Typography style: SF-like.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use Apple's trademarked iMessage lockup in ads — organic pastiche is the usual risk level. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>X-021</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Packet loss packed lunch</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: iMessage conversation with 'Your ISP'. Grey bubble: 'it's not you it's packet loss.'
+On-screen text, large and bold, exactly as written, no other wording added: "Delivered" "read at 19:42" "during the football, obviously"
+Colour palette: iMessage blue/grey, navy end card.
+Typography style: SF-like.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use Apple's trademarked iMessage lockup in ads — organic pastiche is the usual risk level. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>X-022</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Greggs vs gigabit</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Café menu: Sausage roll / 70 Mbps. Steak bake / full fibre. Vegan roll / out of contract price.
+On-screen text, large and bold, exactly as written, no other wording added: "TODAY'S SPECIALS" "dignity: sold out"
+Colour palette: Warm bakery, navy footer.
+Typography style: Menu board gothic.
+Logo placement: Footer.
+Avoid: Don't imply Greggs endorses BroadbandPicker. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>X-022</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Greggs vs gigabit</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Café menu: Sausage roll / 70 Mbps. Steak bake / full fibre. Vegan roll / out of contract price.
+On-screen text, large and bold, exactly as written, no other wording added: "TODAY'S SPECIALS" "dignity: sold out"
+Colour palette: Warm bakery, navy footer.
+Typography style: Menu board gothic.
+Logo placement: Footer.
+Avoid: Don't imply Greggs endorses BroadbandPicker. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>X-022</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Greggs vs gigabit</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Café menu: Sausage roll / 70 Mbps. Steak bake / full fibre. Vegan roll / out of contract price.
+On-screen text, large and bold, exactly as written, no other wording added: "TODAY'S SPECIALS" "dignity: sold out"
+Colour palette: Warm bakery, navy footer.
+Typography style: Menu board gothic.
+Logo placement: Footer.
+Avoid: Don't imply Greggs endorses BroadbandPicker. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>X-023</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TfL delay board</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Dot-matrix board: WIFI  delayed  84 min. Reason: CUPBOARD. A tiny wifi mark as the operator.
+On-screen text, large and bold, exactly as written, no other wording added: "WIFI" "Delayed" "Signalling problems in the cupboard"
+Colour palette: Departure-board orange on black, sky-blue end card.
+Typography style: Dot matrix / LED.
+Logo placement: As the 'operator' code BBP.
+Avoid: Don't use the TfL roundel or Johnston type commercially if you're running ads — organic pastiche, original type. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>X-023</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TfL delay board</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Dot-matrix board: WIFI  delayed  84 min. Reason: CUPBOARD. A tiny wifi mark as the operator.
+On-screen text, large and bold, exactly as written, no other wording added: "WIFI" "Delayed" "Signalling problems in the cupboard"
+Colour palette: Departure-board orange on black, sky-blue end card.
+Typography style: Dot matrix / LED.
+Logo placement: As the 'operator' code BBP.
+Avoid: Don't use the TfL roundel or Johnston type commercially if you're running ads — organic pastiche, original type. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>X-023</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TfL delay board</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Dot-matrix board: WIFI  delayed  84 min. Reason: CUPBOARD. A tiny wifi mark as the operator.
+On-screen text, large and bold, exactly as written, no other wording added: "WIFI" "Delayed" "Signalling problems in the cupboard"
+Colour palette: Departure-board orange on black, sky-blue end card.
+Typography style: Dot matrix / LED.
+Logo placement: As the 'operator' code BBP.
+Avoid: Don't use the TfL roundel or Johnston type commercially if you're running ads — organic pastiche, original type. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>X-023</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TfL delay board</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Dot-matrix board: WIFI  delayed  84 min. Reason: CUPBOARD. A tiny wifi mark as the operator.
+On-screen text, large and bold, exactly as written, no other wording added: "WIFI" "Delayed" "Signalling problems in the cupboard"
+Colour palette: Departure-board orange on black, sky-blue end card.
+Typography style: Dot matrix / LED.
+Logo placement: As the 'operator' code BBP.
+Avoid: Don't use the TfL roundel or Johnston type commercially if you're running ads — organic pastiche, original type. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>X-023</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TfL delay board</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Dot-matrix board: WIFI  delayed  84 min. Reason: CUPBOARD. A tiny wifi mark as the operator.
+On-screen text, large and bold, exactly as written, no other wording added: "WIFI" "Delayed" "Signalling problems in the cupboard"
+Colour palette: Departure-board orange on black, sky-blue end card.
+Typography style: Dot matrix / LED.
+Logo placement: As the 'operator' code BBP.
+Avoid: Don't use the TfL roundel or Johnston type commercially if you're running ads — organic pastiche, original type. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>X-024</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Things faster than your broadband</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Medal table. Gold: Nan's gossip. Silver: kettle. Bronze: your download speed, looking ashamed.
+On-screen text, large and bold, exactly as written, no other wording added: "MEDAL TABLE" "household events"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Sports graphic.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use BBC branding. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>X-024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Things faster than your broadband</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Medal table. Gold: Nan's gossip. Silver: kettle. Bronze: your download speed, looking ashamed.
+On-screen text, large and bold, exactly as written, no other wording added: "MEDAL TABLE" "household events"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Sports graphic.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use BBC branding. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>X-024</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Things faster than your broadband</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Medal table. Gold: Nan's gossip. Silver: kettle. Bronze: your download speed, looking ashamed.
+On-screen text, large and bold, exactly as written, no other wording added: "MEDAL TABLE" "household events"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Sports graphic.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use BBC branding. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>X-025</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Providers: we will list you anyway</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Clean navy pages: 1) we list you anyway 2) methodology 3) contact. Looks like a mini media kit.
+On-screen text, large and bold, exactly as written, no other wording added: "We list providers with or without an affiliate deal" "partnerships@broadbandpicker.co.uk"
+Colour palette: Navy #0F172A, sky #0EA5E9, white.
+Typography style: Inter only. B2B, not meme.
+Logo placement: Header on every page.
+Avoid: Don't use sarcasm so hard that a partnerships manager thinks you're unserious. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>X-026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2am vs 7pm speed test</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two phones. Nightstand 2am: huge number. Sofa 7pm: a number that wants to go home.
+On-screen text, large and bold, exactly as written, no other wording added: "02:00" "19:00" "same house, different country"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: App UI + Inter captions.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a provider's official speed-test result page. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>X-026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2am vs 7pm speed test</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two phones. Nightstand 2am: huge number. Sofa 7pm: a number that wants to go home.
+On-screen text, large and bold, exactly as written, no other wording added: "02:00" "19:00" "same house, different country"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: App UI + Inter captions.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a provider's official speed-test result page. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>X-026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2am vs 7pm speed test</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two phones. Nightstand 2am: huge number. Sofa 7pm: a number that wants to go home.
+On-screen text, large and bold, exactly as written, no other wording added: "02:00" "19:00" "same house, different country"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: App UI + Inter captions.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a provider's official speed-test result page. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>X-026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2am vs 7pm speed test</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Two phones. Nightstand 2am: huge number. Sofa 7pm: a number that wants to go home.
+On-screen text, large and bold, exactly as written, no other wording added: "02:00" "19:00" "same house, different country"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: App UI + Inter captions.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't fake a provider's official speed-test result page. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>X-027</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hell is other people's Netflix</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Orange-spine book cover: HELL IS OTHER PEOPLE'S NETFLIX. Author: your ping.
+On-screen text, large and bold, exactly as written, no other wording added: "HELL IS OTHER PEOPLE'S NETFLIX"
+Colour palette: Penguin orange, navy, cream.
+Typography style: A literary grotesque. Not the real Penguin lockup.
+Logo placement: Tiny.
+Avoid: Don't copy Penguin's colophon. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>X-027</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hell is other people's Netflix</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Orange-spine book cover: HELL IS OTHER PEOPLE'S NETFLIX. Author: your ping.
+On-screen text, large and bold, exactly as written, no other wording added: "HELL IS OTHER PEOPLE'S NETFLIX"
+Colour palette: Penguin orange, navy, cream.
+Typography style: A literary grotesque. Not the real Penguin lockup.
+Logo placement: Tiny.
+Avoid: Don't copy Penguin's colophon. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>X-027</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hell is other people's Netflix</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Orange-spine book cover: HELL IS OTHER PEOPLE'S NETFLIX. Author: your ping.
+On-screen text, large and bold, exactly as written, no other wording added: "HELL IS OTHER PEOPLE'S NETFLIX"
+Colour palette: Penguin orange, navy, cream.
+Typography style: A literary grotesque. Not the real Penguin lockup.
+Logo placement: Tiny.
+Avoid: Don't copy Penguin's colophon. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>X-027</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hell is other people's Netflix</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Orange-spine book cover: HELL IS OTHER PEOPLE'S NETFLIX. Author: your ping.
+On-screen text, large and bold, exactly as written, no other wording added: "HELL IS OTHER PEOPLE'S NETFLIX"
+Colour palette: Penguin orange, navy, cream.
+Typography style: A literary grotesque. Not the real Penguin lockup.
+Logo placement: Tiny.
+Avoid: Don't copy Penguin's colophon. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>X-028</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Moving house broadband</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Sharpie on a moving box. Last item, circled: ACTUALLY CHECK THE POSTCODE.
+On-screen text, large and bold, exactly as written, no other wording added: "Kettle" "Wi-Fi" "Sofa (optional)"
+Colour palette: Cardboard, navy sharpie, sky circle.
+Typography style: Handwritten then Inter CTA.
+Logo placement: Tape-style end card.
+Avoid: Don't show a real new address. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>X-028</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Moving house broadband</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Sharpie on a moving box. Last item, circled: ACTUALLY CHECK THE POSTCODE.
+On-screen text, large and bold, exactly as written, no other wording added: "Kettle" "Wi-Fi" "Sofa (optional)"
+Colour palette: Cardboard, navy sharpie, sky circle.
+Typography style: Handwritten then Inter CTA.
+Logo placement: Tape-style end card.
+Avoid: Don't show a real new address. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>X-028</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Moving house broadband</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Sharpie on a moving box. Last item, circled: ACTUALLY CHECK THE POSTCODE.
+On-screen text, large and bold, exactly as written, no other wording added: "Kettle" "Wi-Fi" "Sofa (optional)"
+Colour palette: Cardboard, navy sharpie, sky circle.
+Typography style: Handwritten then Inter CTA.
+Logo placement: Tape-style end card.
+Avoid: Don't show a real new address. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>X-028</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Moving house broadband</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Sharpie on a moving box. Last item, circled: ACTUALLY CHECK THE POSTCODE.
+On-screen text, large and bold, exactly as written, no other wording added: "Kettle" "Wi-Fi" "Sofa (optional)"
+Colour palette: Cardboard, navy sharpie, sky circle.
+Typography style: Handwritten then Inter CTA.
+Logo placement: Tape-style end card.
+Avoid: Don't show a real new address. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>X-029</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Chatbot of Theseus</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Generic chat bubbles. The bot remains cheerfully useless. A 'human' button that is greyed out until 2029.
+On-screen text, large and bold, exactly as written, no other wording added: "Have you tried restarting yourself?"
+Colour palette: Chat greys, navy end.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real ISP's chatbot skin. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>X-029</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Chatbot of Theseus</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Generic chat bubbles. The bot remains cheerfully useless. A 'human' button that is greyed out until 2029.
+On-screen text, large and bold, exactly as written, no other wording added: "Have you tried restarting yourself?"
+Colour palette: Chat greys, navy end.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real ISP's chatbot skin. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>X-029</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Chatbot of Theseus</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Generic chat bubbles. The bot remains cheerfully useless. A 'human' button that is greyed out until 2029.
+On-screen text, large and bold, exactly as written, no other wording added: "Have you tried restarting yourself?"
+Colour palette: Chat greys, navy end.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real ISP's chatbot skin. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>X-029</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Chatbot of Theseus</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Generic chat bubbles. The bot remains cheerfully useless. A 'human' button that is greyed out until 2029.
+On-screen text, large and bold, exactly as written, no other wording added: "Have you tried restarting yourself?"
+Colour palette: Chat greys, navy end.
+Typography style: UI type.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't use a real ISP's chatbot skin. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>X-030</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Broad band</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Souvenir tea towel: It's called broadband because the bills are. Red, white, sky blue. Deeply sincere kitsch.
+On-screen text, large and bold, exactly as written, no other wording added: "IT'S CALLED BROADBAND BECAUSE THE BILLS ARE"
+Colour palette: Kitsch Union-adjacent colours without using the flag as a prop if it feels shouty — navy/sky/white is enough.
+Typography style: Tea-towel serif.
+Logo placement: Woven in the corner.
+Avoid: Don't actually print it until trademarks and jokes are cleared. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>X-030</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Broad band</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Souvenir tea towel: It's called broadband because the bills are. Red, white, sky blue. Deeply sincere kitsch.
+On-screen text, large and bold, exactly as written, no other wording added: "IT'S CALLED BROADBAND BECAUSE THE BILLS ARE"
+Colour palette: Kitsch Union-adjacent colours without using the flag as a prop if it feels shouty — navy/sky/white is enough.
+Typography style: Tea-towel serif.
+Logo placement: Woven in the corner.
+Avoid: Don't actually print it until trademarks and jokes are cleared. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>X-030</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Broad band</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Souvenir tea towel: It's called broadband because the bills are. Red, white, sky blue. Deeply sincere kitsch.
+On-screen text, large and bold, exactly as written, no other wording added: "IT'S CALLED BROADBAND BECAUSE THE BILLS ARE"
+Colour palette: Kitsch Union-adjacent colours without using the flag as a prop if it feels shouty — navy/sky/white is enough.
+Typography style: Tea-towel serif.
+Logo placement: Woven in the corner.
+Avoid: Don't actually print it until trademarks and jokes are cleared. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>X-031</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Poll: who is the IT department</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four illustrated household saints. Steve has a halo of Ethernet.
+On-screen text, large and bold, exactly as written, no other wording added: "WHO IS IT SUPPORT" "tag them"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Corner.
+Avoid: Don't hide the poll under a 400-word caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>X-031</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Poll: who is the IT department</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four illustrated household saints. Steve has a halo of Ethernet.
+On-screen text, large and bold, exactly as written, no other wording added: "WHO IS IT SUPPORT" "tag them"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Corner.
+Avoid: Don't hide the poll under a 400-word caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>X-031</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Poll: who is the IT department</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four illustrated household saints. Steve has a halo of Ethernet.
+On-screen text, large and bold, exactly as written, no other wording added: "WHO IS IT SUPPORT" "tag them"
+Colour palette: Navy #0F172A background, sky #0EA5E9 highlights, white type, green #22C55E only for a genuine 'good news' sting. High contrast, no grey-on-grey.
+Typography style: Inter.
+Logo placement: Corner.
+Avoid: Don't hide the poll under a 400-word caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>X-032</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Rural Yeti van</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Pub table, beer mat sketch of a van labelled FIBRE. Like a cryptid sighting.
+On-screen text, large and bold, exactly as written, no other wording added: "SIGHTING" "unconfirmed" "third pint"
+Colour palette: Pub wood, navy caption.
+Typography style: BiRo handwriting.
+Logo placement: Beer-mat corner.
+Avoid: Don't mock rural users as backward — mock the promises. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>X-032</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Rural Yeti van</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Pub table, beer mat sketch of a van labelled FIBRE. Like a cryptid sighting.
+On-screen text, large and bold, exactly as written, no other wording added: "SIGHTING" "unconfirmed" "third pint"
+Colour palette: Pub wood, navy caption.
+Typography style: BiRo handwriting.
+Logo placement: Beer-mat corner.
+Avoid: Don't mock rural users as backward — mock the promises. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>X-033</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Expanding brain</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four-panel brain. Final panel is the BroadbandPicker postcode box glowing like the holy grail.
+On-screen text, large and bold, exactly as written, no other wording added: "restart" "shout" "4G window" "switch like an adult"
+Colour palette: Meme-native, brand on last panel only.
+Typography style: Impact.
+Logo placement: Last panel UI.
+Avoid: Don't make the first three panels so funny that nobody reads the fourth. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>X-033</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Expanding brain</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four-panel brain. Final panel is the BroadbandPicker postcode box glowing like the holy grail.
+On-screen text, large and bold, exactly as written, no other wording added: "restart" "shout" "4G window" "switch like an adult"
+Colour palette: Meme-native, brand on last panel only.
+Typography style: Impact.
+Logo placement: Last panel UI.
+Avoid: Don't make the first three panels so funny that nobody reads the fourth. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>X-033</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Expanding brain</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four-panel brain. Final panel is the BroadbandPicker postcode box glowing like the holy grail.
+On-screen text, large and bold, exactly as written, no other wording added: "restart" "shout" "4G window" "switch like an adult"
+Colour palette: Meme-native, brand on last panel only.
+Typography style: Impact.
+Logo placement: Last panel UI.
+Avoid: Don't make the first three panels so funny that nobody reads the fourth. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>X-033</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Expanding brain</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Four-panel brain. Final panel is the BroadbandPicker postcode box glowing like the holy grail.
+On-screen text, large and bold, exactly as written, no other wording added: "restart" "shout" "4G window" "switch like an adult"
+Colour palette: Meme-native, brand on last panel only.
+Typography style: Impact.
+Logo placement: Last panel UI.
+Avoid: Don't make the first three panels so funny that nobody reads the fourth. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>X-034</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Awin-ready publisher energy</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Simple stat tiles from the workspace: provider count, guide count, trust pages live.
+On-screen text, large and bold, exactly as written, no other wording added: "Independent comparison" "Affiliate-honest" "Built for UK broadband"
+Colour palette: Navy #0F172A + sky #0EA5E9.
+Typography style: Inter ExtraBold.
+Logo placement: Top-left.
+Avoid: Don't put meme Impact font on LinkedIn. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>X-035</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Black Friday is not a personality</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Screaming red SALE graphics that peel off to reveal a boring navy fact about postcodes.
+On-screen text, large and bold, exactly as written, no other wording added: "40% OFF" "the same cabinet" "check the postcode"
+Colour palette: Sale red then brand navy — the point is the peel.
+Typography style: Shouty then Inter.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't run unverified 'from £x' in the caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>X-035</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Black Friday is not a personality</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Screaming red SALE graphics that peel off to reveal a boring navy fact about postcodes.
+On-screen text, large and bold, exactly as written, no other wording added: "40% OFF" "the same cabinet" "check the postcode"
+Colour palette: Sale red then brand navy — the point is the peel.
+Typography style: Shouty then Inter.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't run unverified 'from £x' in the caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>X-035</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Black Friday is not a personality</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>TikTok cover / first frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for TikTok cover / first frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Screaming red SALE graphics that peel off to reveal a boring navy fact about postcodes.
+On-screen text, large and bold, exactly as written, no other wording added: "40% OFF" "the same cabinet" "check the postcode"
+Colour palette: Sale red then brand navy — the point is the peel.
+Typography style: Shouty then Inter.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't run unverified 'from £x' in the caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>X-035</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Black Friday is not a personality</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Screaming red SALE graphics that peel off to reveal a boring navy fact about postcodes.
+On-screen text, large and bold, exactly as written, no other wording added: "40% OFF" "the same cabinet" "check the postcode"
+Colour palette: Sale red then brand navy — the point is the peel.
+Typography style: Shouty then Inter.
+Logo placement: Native joke first, brand last. Wifi-mark + wordmark on a 0.4s end card or bottom-left safe zone. Never put the logo over the punchline.
+Avoid: Don't run unverified 'from £x' in the caption. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>X-036</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>To switch or not to switch</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Instagram feed post (4:5)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1080x1350px</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1350px graphic for Instagram feed post (4:5), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Fake First Folio page. Stage direction: Enter ROUTER, blinking. Derek, on the sofa, pays £41.
+On-screen text, large and bold, exactly as written, no other wording added: "To switch, or not to switch" "Enter ROUTER"
+Colour palette: Aged paper, blackletter-ish (readable), sky stage directions.
+Typography style: A readable old-style serif, not unreadable blackletter.
+Logo placement: Printer's mark wifi icon.
+Avoid: Don't make it so 'designy' that nobody reads Derek. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>X-036</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>To switch or not to switch</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Instagram quote card (1:1)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1080x1080px</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1080px graphic for Instagram quote card (1:1), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Fake First Folio page. Stage direction: Enter ROUTER, blinking. Derek, on the sofa, pays £41.
+On-screen text, large and bold, exactly as written, no other wording added: "To switch, or not to switch" "Enter ROUTER"
+Colour palette: Aged paper, blackletter-ish (readable), sky stage directions.
+Typography style: A readable old-style serif, not unreadable blackletter.
+Logo placement: Printer's mark wifi icon.
+Avoid: Don't make it so 'designy' that nobody reads Derek. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>X-036</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>To switch or not to switch</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Instagram Reel/Story cover frame (9:16)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1080x1920px</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1080x1920px graphic for Instagram Reel/Story cover frame (9:16), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Fake First Folio page. Stage direction: Enter ROUTER, blinking. Derek, on the sofa, pays £41.
+On-screen text, large and bold, exactly as written, no other wording added: "To switch, or not to switch" "Enter ROUTER"
+Colour palette: Aged paper, blackletter-ish (readable), sky stage directions.
+Typography style: A readable old-style serif, not unreadable blackletter.
+Logo placement: Printer's mark wifi icon.
+Avoid: Don't make it so 'designy' that nobody reads Derek. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>X-036</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>To switch or not to switch</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>X post image (16:9)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1600x900px</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Create a 1600x900px graphic for X post image (16:9), for BroadbandPicker, an independent UK broadband comparison brand — witty British deadpan tone, not corporate, not cringe.
+Concept: Fake First Folio page. Stage direction: Enter ROUTER, blinking. Derek, on the sofa, pays £41.
+On-screen text, large and bold, exactly as written, no other wording added: "To switch, or not to switch" "Enter ROUTER"
+Colour palette: Aged paper, blackletter-ish (readable), sky stage directions.
+Typography style: A readable old-style serif, not unreadable blackletter.
+Logo placement: Printer's mark wifi icon.
+Avoid: Don't make it so 'designy' that nobody reads Derek. No stock-photo faces. No fake provider logos or trademarks.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>